--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.78063996715417</v>
+        <v>6.139353994662552</v>
       </c>
       <c r="D2" t="n">
-        <v>38.0049063322481</v>
+        <v>6.175797278990317</v>
       </c>
       <c r="E2" t="n">
-        <v>9.958851601765632</v>
+        <v>1.618313385286915</v>
       </c>
       <c r="F2" t="n">
-        <v>9.585891332062207</v>
+        <v>1.557707341460109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06093891603233</v>
+        <v>4.397402573855254</v>
       </c>
       <c r="D3" t="n">
-        <v>26.8954912528102</v>
+        <v>4.370517328581657</v>
       </c>
       <c r="E3" t="n">
-        <v>9.958851601765632</v>
+        <v>1.618313385286915</v>
       </c>
       <c r="F3" t="n">
-        <v>9.585891332062207</v>
+        <v>1.557707341460109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.0162042589814</v>
+        <v>3.902633192084477</v>
       </c>
       <c r="D4" t="n">
-        <v>26.10236056453164</v>
+        <v>4.241633591736391</v>
       </c>
       <c r="E4" t="n">
-        <v>9.958851601765632</v>
+        <v>1.618313385286915</v>
       </c>
       <c r="F4" t="n">
-        <v>9.585891332062207</v>
+        <v>1.557707341460109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.95244410750542</v>
+        <v>2.917272167469632</v>
       </c>
       <c r="D5" t="n">
-        <v>19.10936629084264</v>
+        <v>3.10527202226193</v>
       </c>
       <c r="E5" t="n">
-        <v>9.958851601765632</v>
+        <v>1.618313385286915</v>
       </c>
       <c r="F5" t="n">
-        <v>9.585891332062207</v>
+        <v>1.557707341460109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.7176922189991</v>
+        <v>7.429124985587355</v>
       </c>
       <c r="D6" t="n">
-        <v>46.11482374007469</v>
+        <v>7.493658857762138</v>
       </c>
       <c r="E6" t="n">
-        <v>9.958851601765632</v>
+        <v>1.618313385286915</v>
       </c>
       <c r="F6" t="n">
-        <v>9.585891332062207</v>
+        <v>1.557707341460109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
